--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/COLORADO_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/COLORADO_2016.xlsx
@@ -2940,7 +2940,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C144">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C193">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C313">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C770">
